--- a/utils/data-room-simulator/output/salary_bands.xlsx
+++ b/utils/data-room-simulator/output/salary_bands.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Salary Bands" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Salary Bands" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,27 +417,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>salary_band</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>headcount</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>total_salary</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>avg_salary</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_of_total</t>
         </is>
@@ -462,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1300676</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>43355.87</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C3" t="n">
-        <v>845436.63</v>
+        <v>2162835.49</v>
       </c>
       <c r="D3" t="n">
-        <v>70453.05</v>
+        <v>63612.81</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>2551359.87</v>
+        <v>2765780.64</v>
       </c>
       <c r="D4" t="n">
-        <v>87977.92999999999</v>
+        <v>86430.64</v>
       </c>
       <c r="E4" t="n">
-        <v>14.6</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +507,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C5" t="n">
-        <v>4717449.05</v>
+        <v>7070971.61</v>
       </c>
       <c r="D5" t="n">
-        <v>124143.4</v>
+        <v>119846.98</v>
       </c>
       <c r="E5" t="n">
-        <v>19.2</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +526,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>7087697.12</v>
+        <v>3986122.68</v>
       </c>
       <c r="D6" t="n">
-        <v>177192.43</v>
+        <v>166088.44</v>
       </c>
       <c r="E6" t="n">
-        <v>20.2</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +545,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>21764473.16</v>
+        <v>1572637.67</v>
       </c>
       <c r="D7" t="n">
-        <v>275499.66</v>
+        <v>224662.52</v>
       </c>
       <c r="E7" t="n">
-        <v>39.9</v>
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>
